--- a/Unity/GameData/DataTables/UITable.xlsx
+++ b/Unity/GameData/DataTables/UITable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>#</t>
   </si>
@@ -84,6 +84,12 @@
   </si>
   <si>
     <t>CommonUI</t>
+  </si>
+  <si>
+    <t>DialogForm</t>
+  </si>
+  <si>
+    <t>PopupUI</t>
   </si>
 </sst>
 </file>
@@ -702,8 +708,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1237,8 +1244,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5" outlineLevelCol="6"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1339,6 +1346,23 @@
         <v>0</v>
       </c>
       <c r="G6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Unity/GameData/DataTables/UITable.xlsx
+++ b/Unity/GameData/DataTables/UITable.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="11655"/>
+    <workbookView windowHeight="19160"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
   <si>
     <t>#</t>
   </si>
@@ -47,6 +47,9 @@
     <t>Priority</t>
   </si>
   <si>
+    <t>AllowMultiInstance</t>
+  </si>
+  <si>
     <t>PauseCovered</t>
   </si>
   <si>
@@ -69,6 +72,9 @@
   </si>
   <si>
     <t>加载界面资源的优先级</t>
+  </si>
+  <si>
+    <t>是否允许多个界面实例</t>
   </si>
   <si>
     <t>是否暂停被覆盖的界面</t>
@@ -1231,10 +1237,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="4" outlineLevelCol="6"/>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="7"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1242,7 +1248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1261,70 +1267,82 @@
       <c r="G2" t="s">
         <v>6</v>
       </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
       <c r="G3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="1:8">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="D1:Z1">
+    <dataValidation type="list" allowBlank="1" sqref="D1:AA1">
       <formula1>"i18n"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E3:Z3">
+    <dataValidation type="list" sqref="E3:AA3">
       <formula1>"bool,byte,char,Color,Color32,DateTime,decimal,double,float,int,long,Quaternion,Rect,sbyte,short,string,uint,ulong,ushort,Vector2,Vector3,Vector4"</formula1>
     </dataValidation>
   </dataValidations>
